--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>10</v>
@@ -450,7 +450,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>832</v>
@@ -459,7 +459,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>852</v>
